--- a/ig/DM-SIDOBA/ValueSet-jdv-j411-esms-adulte-medicalise-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j411-esms-adulte-medicalise-ms.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j411-esms-adulte--medicalise-ms</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j411-esms-adulte-medicalise-ms</t>
   </si>
   <si>
     <t>Identifier</t>
